--- a/data/trans_orig/IMC_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2007</t>
+          <t>Población con sobrepeso u obesidad en 2007 (tasa de respuesta: 98,86%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>665681</t>
+          <t>664917</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>727018</t>
+          <t>724264</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,8%</t>
+          <t>71,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>850636</t>
+          <t>851614</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>916657</t>
+          <t>923307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,19%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,33%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1537561</t>
+          <t>1538760</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1627937</t>
+          <t>1628758</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,92%</t>
+          <t>66,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>285522</t>
+          <t>288276</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>346859</t>
+          <t>347623</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>368428</t>
+          <t>361778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>434449</t>
+          <t>433471</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,67%</t>
+          <t>28,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,81%</t>
+          <t>33,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>669688</t>
+          <t>668867</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>760064</t>
+          <t>758865</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,15%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,03%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>890735</t>
+          <t>891754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>972717</t>
+          <t>971133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,65%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>522516</t>
+          <t>520007</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>596050</t>
+          <t>596867</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,17%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1430571</t>
+          <t>1434436</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1542433</t>
+          <t>1546130</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>44,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>711856</t>
+          <t>713440</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>793838</t>
+          <t>792819</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>42,35%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>47,06%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>979255</t>
+          <t>978438</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1052789</t>
+          <t>1055298</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,11%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,83%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1717446</t>
+          <t>1713749</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1829308</t>
+          <t>1825443</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,68%</t>
+          <t>52,57%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>56,0%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>270845</t>
+          <t>270787</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>320055</t>
+          <t>321273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>110675</t>
+          <t>112163</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150870</t>
+          <t>150351</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>394339</t>
+          <t>395504</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>460743</t>
+          <t>459264</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,68%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,19%</t>
+          <t>45,05%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226910</t>
+          <t>225692</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276120</t>
+          <t>276178</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>321718</t>
+          <t>322237</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>361913</t>
+          <t>360425</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>68,19%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,58%</t>
+          <t>76,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>558810</t>
+          <t>560289</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>625214</t>
+          <t>624049</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,21%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1870667</t>
+          <t>1866586</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1980387</t>
+          <t>1979827</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1514167</t>
+          <t>1515368</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1636648</t>
+          <t>1632779</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,43%</t>
+          <t>45,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>48,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3408281</t>
+          <t>3418548</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3574539</t>
+          <t>3579984</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>54,43%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1263692</t>
+          <t>1264252</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1373412</t>
+          <t>1377493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,95%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1696330</t>
+          <t>1700199</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1818811</t>
+          <t>1817610</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>50,9%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3002518</t>
+          <t>2997073</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3168776</t>
+          <t>3158509</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>45,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>48,02%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2012</t>
+          <t>Población con sobrepeso u obesidad en 2012 (tasa de respuesta: 96,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>657956</t>
+          <t>661056</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>716247</t>
+          <t>713759</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,21%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,07%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>896507</t>
+          <t>898036</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>958399</t>
+          <t>962151</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>77,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1575521</t>
+          <t>1574531</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1652799</t>
+          <t>1661690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,33%</t>
+          <t>72,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225314</t>
+          <t>227802</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283605</t>
+          <t>280505</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,93%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>278258</t>
+          <t>274506</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>340150</t>
+          <t>338621</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>525418</t>
+          <t>516527</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>602696</t>
+          <t>603686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,12%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,71%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1187707</t>
+          <t>1185860</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1274904</t>
+          <t>1270907</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>65,48%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>744711</t>
+          <t>747848</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>830876</t>
+          <t>826887</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,49%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1949857</t>
+          <t>1946650</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2076959</t>
+          <t>2070816</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,85%</t>
+          <t>56,69%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>665975</t>
+          <t>669972</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>753172</t>
+          <t>755019</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>34,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,81%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>881382</t>
+          <t>885371</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>967547</t>
+          <t>964410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1576177</t>
+          <t>1582320</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1703279</t>
+          <t>1706486</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,15%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,71%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253601</t>
+          <t>253025</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>298215</t>
+          <t>299877</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>53,61%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112902</t>
+          <t>113743</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>153430</t>
+          <t>154815</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>33,75%</t>
+          <t>34,06%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>376350</t>
+          <t>377935</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>443495</t>
+          <t>443127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,83%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>173719</t>
+          <t>172057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218333</t>
+          <t>218909</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>301118</t>
+          <t>299733</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341646</t>
+          <t>340805</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>66,25%</t>
+          <t>65,94%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>482987</t>
+          <t>483355</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>550132</t>
+          <t>548547</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,21%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2139221</t>
+          <t>2137161</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2260635</t>
+          <t>2248259</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,39%</t>
+          <t>67,02%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1784164</t>
+          <t>1790931</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1905933</t>
+          <t>1909836</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3960159</t>
+          <t>3961076</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4123043</t>
+          <t>4128824</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,6%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,1%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1093738</t>
+          <t>1106114</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1215152</t>
+          <t>1217212</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,61%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1497530</t>
+          <t>1493627</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1619299</t>
+          <t>1612532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2634792</t>
+          <t>2629011</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2797676</t>
+          <t>2796759</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,4%</t>
+          <t>41,39%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2016</t>
+          <t>Población con sobrepeso u obesidad en 2016 (tasa de respuesta: 95,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>501429</t>
+          <t>500651</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>547357</t>
+          <t>546022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,39%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>623288</t>
+          <t>618608</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>674853</t>
+          <t>674020</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,54%</t>
+          <t>70,01%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1132497</t>
+          <t>1134595</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1209706</t>
+          <t>1205826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,01%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,61%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>163862</t>
+          <t>165197</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>209790</t>
+          <t>210568</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>208792</t>
+          <t>209625</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>260357</t>
+          <t>265037</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,46%</t>
+          <t>29,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>385158</t>
+          <t>389038</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>462367</t>
+          <t>460269</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,86%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1130541</t>
+          <t>1130609</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1218421</t>
+          <t>1219984</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4302,7 +4302,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,53%</t>
+          <t>60,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>862235</t>
+          <t>864312</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>954152</t>
+          <t>952006</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>44,96%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,63%</t>
+          <t>49,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2014416</t>
+          <t>2018722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2136034</t>
+          <t>2148843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,18%</t>
+          <t>51,29%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,6%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>794648</t>
+          <t>793085</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>882528</t>
+          <t>882460</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,7 +4410,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>968358</t>
+          <t>970504</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1060275</t>
+          <t>1058198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,37%</t>
+          <t>50,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,15%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1799545</t>
+          <t>1786736</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1921163</t>
+          <t>1916857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,82%</t>
+          <t>48,71%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>256590</t>
+          <t>254463</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>303265</t>
+          <t>305078</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>48,15%</t>
+          <t>47,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>57,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>163603</t>
+          <t>165378</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208713</t>
+          <t>208256</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>433289</t>
+          <t>435961</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>500399</t>
+          <t>501006</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>47,42%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>229630</t>
+          <t>227817</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276305</t>
+          <t>278432</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>52,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315019</t>
+          <t>315476</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>360129</t>
+          <t>358354</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,76%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>556228</t>
+          <t>555621</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>623338</t>
+          <t>620666</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,64%</t>
+          <t>52,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,74%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1930427</t>
+          <t>1926659</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2038171</t>
+          <t>2035985</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>59,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,51%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1681559</t>
+          <t>1683467</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1795222</t>
+          <t>1800318</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,91%</t>
+          <t>54,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3641511</t>
+          <t>3642191</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3805657</t>
+          <t>3802574</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,73%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1219012</t>
+          <t>1221198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1326756</t>
+          <t>1330524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>37,49%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,73%</t>
+          <t>40,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1534665</t>
+          <t>1529569</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1648328</t>
+          <t>1646420</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>45,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2781413</t>
+          <t>2784496</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2945559</t>
+          <t>2944879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>44,71%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con sobrepeso u obesidad en 2023</t>
+          <t>Población con sobrepeso u obesidad en 2023 (tasa de respuesta: 96,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>352144</t>
+          <t>353949</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>387215</t>
+          <t>388886</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>72,14%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,92%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>494054</t>
+          <t>493559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>529962</t>
+          <t>530343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,97%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>857395</t>
+          <t>857005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>908364</t>
+          <t>908258</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,0%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103413</t>
+          <t>101742</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>138484</t>
+          <t>136679</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>21,08%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>159043</t>
+          <t>158662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>194951</t>
+          <t>195446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271270</t>
+          <t>271376</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322239</t>
+          <t>322629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,0%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>27,35%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1355307</t>
+          <t>1356291</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1737017</t>
+          <t>1705936</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,85%</t>
+          <t>59,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>76,71%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1040622</t>
+          <t>1049457</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1472262</t>
+          <t>1490056</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,1%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2462071</t>
+          <t>2463291</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3042506</t>
+          <t>3049410</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>55,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,87%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>527375</t>
+          <t>558456</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>909085</t>
+          <t>908101</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,15%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>691228</t>
+          <t>673434</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1122868</t>
+          <t>1114033</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,9%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1385377</t>
+          <t>1378473</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1965812</t>
+          <t>1964592</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>44,37%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>329904</t>
+          <t>330698</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>390149</t>
+          <t>387535</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>61,36%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>210141</t>
+          <t>211535</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254639</t>
+          <t>254921</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>558252</t>
+          <t>557173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>629139</t>
+          <t>627989</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,18%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>245717</t>
+          <t>248331</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305962</t>
+          <t>305168</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>38,64%</t>
+          <t>39,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>47,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>386313</t>
+          <t>386031</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>430811</t>
+          <t>429417</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,27%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,21%</t>
+          <t>67,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647679</t>
+          <t>648829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>718566</t>
+          <t>719645</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>50,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,28%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2084696</t>
+          <t>2089524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2475608</t>
+          <t>2461197</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1800798</t>
+          <t>1798180</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2268136</t>
+          <t>2277050</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,55%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3920623</t>
+          <t>3915601</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4507354</t>
+          <t>4482208</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,95%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,47%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>915279</t>
+          <t>929690</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1306191</t>
+          <t>1301363</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1225312</t>
+          <t>1216398</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1692650</t>
+          <t>1695268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,45%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2376980</t>
+          <t>2402126</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2963711</t>
+          <t>2968733</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,53%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,05%</t>
+          <t>43,12%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IMC_R2-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IMC_R2-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>664917</t>
+          <t>665514</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>724264</t>
+          <t>724771</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,67%</t>
+          <t>65,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>851614</t>
+          <t>851802</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>923307</t>
+          <t>920039</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,28%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1538760</t>
+          <t>1538033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1628758</t>
+          <t>1626805</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,97%</t>
+          <t>66,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,8%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>288276</t>
+          <t>287769</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>347623</t>
+          <t>347026</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,47%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>34,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>361778</t>
+          <t>365046</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>433471</t>
+          <t>433283</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,72%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>668867</t>
+          <t>670820</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>758865</t>
+          <t>759592</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>29,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,03%</t>
+          <t>33,06%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>891754</t>
+          <t>891323</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>971133</t>
+          <t>973173</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>52,94%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>520007</t>
+          <t>519437</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>596867</t>
+          <t>593562</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1434436</t>
+          <t>1435811</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1546130</t>
+          <t>1543884</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>44,0%</t>
+          <t>44,04%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>47,36%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>713440</t>
+          <t>711400</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>792819</t>
+          <t>793250</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>47,06%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>978438</t>
+          <t>981743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1055298</t>
+          <t>1055868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1713749</t>
+          <t>1715995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1825443</t>
+          <t>1824068</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>52,57%</t>
+          <t>52,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>55,96%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>270787</t>
+          <t>272749</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>321273</t>
+          <t>320580</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>49,51%</t>
+          <t>49,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,61%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>111387</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>150351</t>
+          <t>151848</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>395504</t>
+          <t>393636</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>459264</t>
+          <t>457692</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>38,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,05%</t>
+          <t>44,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>225692</t>
+          <t>226385</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>276178</t>
+          <t>274216</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,49%</t>
+          <t>50,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>322237</t>
+          <t>320740</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>360425</t>
+          <t>361201</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>67,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>560289</t>
+          <t>561861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624049</t>
+          <t>625917</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,95%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1866586</t>
+          <t>1869898</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1979827</t>
+          <t>1981608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,54%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1515368</t>
+          <t>1519462</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1632779</t>
+          <t>1631473</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3418548</t>
+          <t>3422415</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3579984</t>
+          <t>3589263</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,43%</t>
+          <t>54,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1264252</t>
+          <t>1262471</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1377493</t>
+          <t>1374181</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>42,46%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1700199</t>
+          <t>1701505</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1817610</t>
+          <t>1813516</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2997073</t>
+          <t>2987794</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>3158509</t>
+          <t>3154642</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,57%</t>
+          <t>45,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>661056</t>
+          <t>659369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>713759</t>
+          <t>717436</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,21%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,81%</t>
+          <t>76,2%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>898036</t>
+          <t>898413</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>962151</t>
+          <t>960275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,8%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1574531</t>
+          <t>1576952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1661690</t>
+          <t>1660907</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,29%</t>
+          <t>72,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,25%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>227802</t>
+          <t>224125</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>280505</t>
+          <t>282192</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274506</t>
+          <t>276382</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>338621</t>
+          <t>338244</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>516527</t>
+          <t>517310</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>603686</t>
+          <t>601265</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,71%</t>
+          <t>27,6%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1185860</t>
+          <t>1182646</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1270907</t>
+          <t>1269713</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>747848</t>
+          <t>741914</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>826887</t>
+          <t>826591</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,33%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1946650</t>
+          <t>1955935</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2070816</t>
+          <t>2076896</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>53,29%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,85%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>669972</t>
+          <t>671166</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>755019</t>
+          <t>758233</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>34,58%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>885371</t>
+          <t>885667</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>964410</t>
+          <t>970344</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,71%</t>
+          <t>51,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>56,32%</t>
+          <t>56,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1582320</t>
+          <t>1576240</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1706486</t>
+          <t>1697201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,15%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>46,71%</t>
+          <t>46,46%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>253025</t>
+          <t>250889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>299877</t>
+          <t>296846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>53,61%</t>
+          <t>53,16%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>63,54%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>113743</t>
+          <t>111440</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>154815</t>
+          <t>153866</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>377935</t>
+          <t>377874</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>443127</t>
+          <t>442158</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3112,7 +3112,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,83%</t>
+          <t>47,72%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>172057</t>
+          <t>175088</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>218909</t>
+          <t>221045</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,46%</t>
+          <t>37,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>46,84%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>299733</t>
+          <t>300682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>340805</t>
+          <t>343108</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>65,94%</t>
+          <t>66,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>75,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>483355</t>
+          <t>484324</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>548547</t>
+          <t>548608</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>52,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2137161</t>
+          <t>2129022</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2248259</t>
+          <t>2249590</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1790931</t>
+          <t>1786836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1909836</t>
+          <t>1909927</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3961076</t>
+          <t>3956573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4128824</t>
+          <t>4124599</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,03%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1106114</t>
+          <t>1104783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1217212</t>
+          <t>1225351</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>36,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1493627</t>
+          <t>1493536</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1612532</t>
+          <t>1616627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>47,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2629011</t>
+          <t>2633236</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2796759</t>
+          <t>2801262</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>41,39%</t>
+          <t>41,45%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>500651</t>
+          <t>499626</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>546022</t>
+          <t>546581</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>618608</t>
+          <t>620598</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>674020</t>
+          <t>675560</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,28%</t>
+          <t>76,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1134595</t>
+          <t>1136411</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>1205826</t>
+          <t>1207477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>75,71%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>165197</t>
+          <t>164638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>210568</t>
+          <t>211593</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,61%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>209625</t>
+          <t>208085</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>265037</t>
+          <t>263047</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>29,99%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>389038</t>
+          <t>387387</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>460269</t>
+          <t>458453</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,86%</t>
+          <t>28,75%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1130609</t>
+          <t>1131922</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1219984</t>
+          <t>1219687</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>56,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,6%</t>
+          <t>60,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>864312</t>
+          <t>863532</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>952006</t>
+          <t>949110</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2018722</t>
+          <t>2017754</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>2148843</t>
+          <t>2143948</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>51,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>54,6%</t>
+          <t>54,48%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>793085</t>
+          <t>793382</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>882460</t>
+          <t>881147</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,41%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>43,84%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>970504</t>
+          <t>973400</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1058198</t>
+          <t>1058978</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,63%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1786736</t>
+          <t>1791631</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1916857</t>
+          <t>1917825</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,4%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>48,73%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>254463</t>
+          <t>257275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>305078</t>
+          <t>301508</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>48,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>57,25%</t>
+          <t>56,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>165378</t>
+          <t>163853</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208256</t>
+          <t>211131</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>435961</t>
+          <t>434017</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>501006</t>
+          <t>497720</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>47,42%</t>
+          <t>47,1%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>227817</t>
+          <t>231387</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>278432</t>
+          <t>275620</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>42,75%</t>
+          <t>43,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,25%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>315476</t>
+          <t>312601</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>358354</t>
+          <t>359879</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,69%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>555621</t>
+          <t>558907</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>620666</t>
+          <t>622610</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>52,58%</t>
+          <t>52,9%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1926659</t>
+          <t>1927368</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2035985</t>
+          <t>2035204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1683467</t>
+          <t>1683836</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1800318</t>
+          <t>1800200</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,07%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3642191</t>
+          <t>3628009</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3802574</t>
+          <t>3792829</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,29%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>57,73%</t>
+          <t>57,58%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1221198</t>
+          <t>1221979</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1330524</t>
+          <t>1329815</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,83%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1529569</t>
+          <t>1529687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1646420</t>
+          <t>1646051</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,93%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2784496</t>
+          <t>2794241</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2944879</t>
+          <t>2959061</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>42,27%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>44,92%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>371315</t>
+          <t>405441</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>353949</t>
+          <t>386596</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>388886</t>
+          <t>424150</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>71,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>512297</t>
+          <t>561082</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>493559</t>
+          <t>540639</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>530343</t>
+          <t>579229</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>71,63%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>76,97%</t>
+          <t>77,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>883613</t>
+          <t>966523</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>857005</t>
+          <t>937211</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>908258</t>
+          <t>992725</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,65%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,99%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>119313</t>
+          <t>139047</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>101742</t>
+          <t>120338</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>136679</t>
+          <t>157892</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>29,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>176708</t>
+          <t>190070</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>158662</t>
+          <t>171923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195446</t>
+          <t>210513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>28,37%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>296021</t>
+          <t>329117</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>271376</t>
+          <t>302915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>322629</t>
+          <t>358429</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>23,01%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,35%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>490628</t>
+          <t>544488</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>490628</t>
+          <t>544488</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>490628</t>
+          <t>544488</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>689005</t>
+          <t>751152</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>689005</t>
+          <t>751152</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>689005</t>
+          <t>751152</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1179634</t>
+          <t>1295640</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1179634</t>
+          <t>1295640</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1179634</t>
+          <t>1295640</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1471279</t>
+          <t>1332835</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1356291</t>
+          <t>1279283</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1705936</t>
+          <t>1383510</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>60,65%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>62,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1181659</t>
+          <t>1024780</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1049457</t>
+          <t>982320</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1490056</t>
+          <t>1070195</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>50,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>2652939</t>
+          <t>2357615</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2463291</t>
+          <t>2286084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>3049410</t>
+          <t>2422713</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>59,91%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>55,63%</t>
+          <t>52,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>56,09%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>793113</t>
+          <t>864658</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>558456</t>
+          <t>813983</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>908101</t>
+          <t>918210</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>37,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>981831</t>
+          <t>1097065</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>673434</t>
+          <t>1051650</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1114033</t>
+          <t>1139525</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>45,38%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>51,49%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1774944</t>
+          <t>1961724</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1378473</t>
+          <t>1896626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1964592</t>
+          <t>2033255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>40,09%</t>
+          <t>45,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>43,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>44,37%</t>
+          <t>47,07%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2264392</t>
+          <t>2197493</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2264392</t>
+          <t>2197493</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2264392</t>
+          <t>2197493</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2163490</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2163490</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2163490</t>
+          <t>2121845</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>4427883</t>
+          <t>4319339</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4427883</t>
+          <t>4319339</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>4427883</t>
+          <t>4319339</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>360475</t>
+          <t>392190</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>330698</t>
+          <t>362002</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>387535</t>
+          <t>421654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>232958</t>
+          <t>265813</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>211535</t>
+          <t>244768</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>254921</t>
+          <t>291299</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>34,28%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>40,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>593433</t>
+          <t>658002</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>557173</t>
+          <t>622866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>627989</t>
+          <t>697849</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>46,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>44,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>49,39%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>275391</t>
+          <t>306652</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>248331</t>
+          <t>277188</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305168</t>
+          <t>336840</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39,05%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>47,99%</t>
+          <t>48,2%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>407994</t>
+          <t>448259</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>386031</t>
+          <t>422773</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>429417</t>
+          <t>469304</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>59,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>67,0%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>683385</t>
+          <t>754911</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>648829</t>
+          <t>715064</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>719645</t>
+          <t>790047</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>56,36%</t>
+          <t>55,92%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>635866</t>
+          <t>698842</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>635866</t>
+          <t>698842</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>635866</t>
+          <t>698842</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>640952</t>
+          <t>714072</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>640952</t>
+          <t>714072</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>640952</t>
+          <t>714072</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1276818</t>
+          <t>1412913</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1276818</t>
+          <t>1412913</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1276818</t>
+          <t>1412913</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2203071</t>
+          <t>2130465</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2089524</t>
+          <t>2061408</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2461197</t>
+          <t>2194175</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>64,97%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>61,62%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>63,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>1926915</t>
+          <t>1851675</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1798180</t>
+          <t>1799395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2277050</t>
+          <t>1904425</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>50,16%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>65,18%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4129985</t>
+          <t>3982141</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3915601</t>
+          <t>3895791</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4482208</t>
+          <t>4064370</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>59,99%</t>
+          <t>56,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>55,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>65,11%</t>
+          <t>57,83%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1187816</t>
+          <t>1310358</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>929690</t>
+          <t>1246648</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1301363</t>
+          <t>1379415</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>35,03%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>38,38%</t>
+          <t>40,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>1566533</t>
+          <t>1735394</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1216398</t>
+          <t>1682644</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1695268</t>
+          <t>1787674</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>49,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>2754349</t>
+          <t>3045752</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2402126</t>
+          <t>2963523</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>2968733</t>
+          <t>3132102</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>40,01%</t>
+          <t>43,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>34,89%</t>
+          <t>42,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>43,12%</t>
+          <t>44,57%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3390887</t>
+          <t>3440823</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3390887</t>
+          <t>3440823</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3390887</t>
+          <t>3440823</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3493448</t>
+          <t>3587069</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3493448</t>
+          <t>3587069</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>3493448</t>
+          <t>3587069</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>6884334</t>
+          <t>7027893</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>6884334</t>
+          <t>7027893</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>6884334</t>
+          <t>7027893</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
